--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wamp64\www\etec_tcc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1302835-E287-432F-AF89-0B2F680194E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A96071-859D-46CB-9F07-B5DB258F4605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{29DAC051-F374-477C-A375-0284E39B7C14}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha3" sheetId="3" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha3!$A$1:$Q$27</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="282">
   <si>
     <t>Salgadinho de Queijo</t>
   </si>
@@ -317,9 +318,6 @@
     <t>Chá Gelado</t>
   </si>
   <si>
-    <t>Garrafa de chá gelado (500ml)</t>
-  </si>
-  <si>
     <t>../img/chagelado.jpg</t>
   </si>
   <si>
@@ -360,6 +358,534 @@
   </si>
   <si>
     <t>Barra de chocolate ao leite 50g</t>
+  </si>
+  <si>
+    <t>Kitcat</t>
+  </si>
+  <si>
+    <t>8.50</t>
+  </si>
+  <si>
+    <t>Trento Avelã</t>
+  </si>
+  <si>
+    <t>Trento Drak</t>
+  </si>
+  <si>
+    <t>Trento Camarelo</t>
+  </si>
+  <si>
+    <t>Trento Morango</t>
+  </si>
+  <si>
+    <t>Trento Cheesse Morango</t>
+  </si>
+  <si>
+    <t>Trento Chocolate</t>
+  </si>
+  <si>
+    <t>Trento Branco Dark</t>
+  </si>
+  <si>
+    <t>Trento Duo</t>
+  </si>
+  <si>
+    <t>Trento Limão</t>
+  </si>
+  <si>
+    <t>Trento Maracujá</t>
+  </si>
+  <si>
+    <t>Trento Milk</t>
+  </si>
+  <si>
+    <t>Trento Trufa de Maçã</t>
+  </si>
+  <si>
+    <t>Trento Trufa de Chocolate</t>
+  </si>
+  <si>
+    <t>Barra Nutry Avelãs</t>
+  </si>
+  <si>
+    <t>Barra Nutry Morango</t>
+  </si>
+  <si>
+    <t>Barra Nutry Banana</t>
+  </si>
+  <si>
+    <t>Barra Nutry Cajú</t>
+  </si>
+  <si>
+    <t>Barra Nutry Cappucino</t>
+  </si>
+  <si>
+    <t>Barra Nutry Coco</t>
+  </si>
+  <si>
+    <t>Barra Nutry Cookies</t>
+  </si>
+  <si>
+    <t>Barra Nutry Frutas- Vermelhas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biscoito  Nikito Chocolate </t>
+  </si>
+  <si>
+    <t>Biscoito  Nikito Doce de Leite</t>
+  </si>
+  <si>
+    <t>Biscoito  Nikito Morango</t>
+  </si>
+  <si>
+    <t>18.00</t>
+  </si>
+  <si>
+    <t>Tubes Fini Azedinhos</t>
+  </si>
+  <si>
+    <t>Tubes Fini Azedinhos Furtas Silveste</t>
+  </si>
+  <si>
+    <t>Tubes Fini Azedinhos Tutti-Frutti</t>
+  </si>
+  <si>
+    <t>Tubes Fini Azedinhos Uva</t>
+  </si>
+  <si>
+    <t>Melancia Azedinha Fini</t>
+  </si>
+  <si>
+    <t>Dentaduras Fini</t>
+  </si>
+  <si>
+    <t>Minhocas Fini</t>
+  </si>
+  <si>
+    <t>Bala Gelatina Amoras Fini</t>
+  </si>
+  <si>
+    <t>Bala Gelatina Beijos Fini</t>
+  </si>
+  <si>
+    <t>Bala Gelatina Finiburguers Fini</t>
+  </si>
+  <si>
+    <t>Bala Gelatinas Polvo Fini</t>
+  </si>
+  <si>
+    <t>Sonho de Valsa</t>
+  </si>
+  <si>
+    <t>Ouro Branco</t>
+  </si>
+  <si>
+    <t>Bis Xtra</t>
+  </si>
+  <si>
+    <t>Chá Mate Leão Limão</t>
+  </si>
+  <si>
+    <t>Chá Mate Leão Pessego</t>
+  </si>
+  <si>
+    <t>3.19</t>
+  </si>
+  <si>
+    <t>Garrafa de chá gelado  Pessego (1,5l)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Aros de Morango Azedinhos 80g - Fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Bala  Bananas fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Bala  Escovinhas Fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Bala Fini amora.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Bala Fini banana.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Bala fini tubes.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Bala Gelatina Amoras Fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/bala gelatina fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Bala Gelatina Finiburguers Fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Bala Gelatinas Polvo 80g FINI.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/barra nutry avela.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/barra nutry banana.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/barra nutry caju.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/barra nutry cappuccino.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/barra nutry coco.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/barra nutry cookies.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/barra nutry frutas-vermelhas.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/barra nutry morango.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Bis.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/cha mate pessego.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/fini Dentaduras.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/finiMinhocas.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/kitcat.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Melancia Azedinha fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/nikito chocolate.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/nikito doce leite.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/nikito morango.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/ouro branco.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento avelas.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento branco-drak.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento Caramelo.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento cheese morango.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento chocolate 38.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento dark.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento duo.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento limao.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento maracuja.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento milk.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento morango.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento turfa de chocolate.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/tubes fini azedinhos fru_silveste.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/tubes fini azedinhos tuttifrutti.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/tubes fini azedinhos uva.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/tubes fini azedinhos.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/Barra Nutry bolo_chocolate.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/cha mate limão.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/sonhodevalsa.jpeg </t>
+  </si>
+  <si>
+    <t>../img/coca-cola 500ml.jpeg</t>
+  </si>
+  <si>
+    <t>../img/coca-cola zero 500ml.jpeg</t>
+  </si>
+  <si>
+    <t>../img/coca-cola.jpeg</t>
+  </si>
+  <si>
+    <t>../img/coca-cola zero.jpeg</t>
+  </si>
+  <si>
+    <t>../img/fanta.jpeg</t>
+  </si>
+  <si>
+    <t>../img/fanta uva.jpeg</t>
+  </si>
+  <si>
+    <t>../img/sprite.jpeg</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Coca-Cola Zero</t>
+  </si>
+  <si>
+    <t>Sprite</t>
+  </si>
+  <si>
+    <t>Fanta Uva</t>
+  </si>
+  <si>
+    <t>Fanta Laranja</t>
+  </si>
+  <si>
+    <t>4.20</t>
+  </si>
+  <si>
+    <t>6.99</t>
+  </si>
+  <si>
+    <t>3.69</t>
+  </si>
+  <si>
+    <t>3.99</t>
+  </si>
+  <si>
+    <t>4.70</t>
+  </si>
+  <si>
+    <t>Barra Nutry bolo_chocolate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../img/trento trufa Maçã .jpg </t>
+  </si>
+  <si>
+    <t>Coca-Cola 500ml</t>
+  </si>
+  <si>
+    <t>Coca-Cola Zero 500ml</t>
+  </si>
+  <si>
+    <t>Bala fini tubes</t>
+  </si>
+  <si>
+    <t>Bala Fini banana</t>
+  </si>
+  <si>
+    <t>Aros de Morango Azedinhos 80g</t>
+  </si>
+  <si>
+    <t>Bala  Escovinhas Fini</t>
+  </si>
+  <si>
+    <t>Trento</t>
+  </si>
+  <si>
+    <t>Barra Nutry</t>
+  </si>
+  <si>
+    <t>Fini</t>
+  </si>
+  <si>
+    <t>Bombom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Aros de Morango Azedinhos 80g - Fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Bala  Bananas fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Bala  Escovinhas Fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Bala Fini amora.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Bala Fini banana.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Barra Nutry bolo_chocolate.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Bala fini tubes.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Bala Gelatina Amoras Fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/bala gelatina fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Bala Gelatina Finiburguers Fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Bala Gelatinas Polvo 80g FINI.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/barra nutry avela.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/barra nutry banana.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/barra nutry caju.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/barra nutry cappuccino.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/barra nutry coco.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/barra nutry cookies.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/barra nutry frutas-vermelhas.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/barra nutry morango.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Bis.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/cha mate limão.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/cha mate pessego.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/fini Dentaduras.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/finiMinhocas.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/kitcat.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/Melancia Azedinha fini.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/nikito chocolate.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/nikito doce leite.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/nikito morango.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/ouro branco.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/sonhodevalsa.jpeg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento avelas.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento branco-drak.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento Caramelo.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento cheese morango.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento chocolate 38.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento dark.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento duo.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento limao.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento maracuja.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento milk.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento morango.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento trufa Maçã.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/trento turfa de chocolate.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/tubes fini azedinhos fru_silveste.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/tubes fini azedinhos tuttifrutti.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/tubes fini azedinhos uva.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">img/tubes fini azedinhos.jpg </t>
+  </si>
+  <si>
+    <t>img/coca-cola 500ml.jpeg</t>
+  </si>
+  <si>
+    <t>img/coca-cola zero 500ml.jpeg</t>
+  </si>
+  <si>
+    <t>img/coca-cola.jpeg</t>
+  </si>
+  <si>
+    <t>img/coca-cola zero.jpeg</t>
+  </si>
+  <si>
+    <t>img/fanta.jpeg</t>
+  </si>
+  <si>
+    <t>img/fanta uva.jpeg</t>
+  </si>
+  <si>
+    <t>img/sprite.jpeg</t>
   </si>
 </sst>
 </file>
@@ -389,7 +915,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -405,6 +931,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +972,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -451,16 +983,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -784,7 +1321,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -794,7 +1331,7 @@
                   <a14:compatExt spid="_x0000_s3075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6F2856B-D0E2-751B-A341-8CF3647DD9AA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000030C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1020,7 +1557,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1030,7 +1567,7 @@
                   <a14:compatExt spid="_x0000_s3079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{307B95FD-E625-EFE5-F5D2-F91A7728A984}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000070C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1256,7 +1793,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1266,7 +1803,7 @@
                   <a14:compatExt spid="_x0000_s3083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1343F6DC-36CD-A94E-6CDE-B42E71C96DAE}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1492,7 +2029,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>21</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1502,7 +2039,7 @@
                   <a14:compatExt spid="_x0000_s3087"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{285EA0E2-B24F-E213-AC1A-287EFE0BF9B6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1728,7 +2265,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>10</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1738,7 +2275,7 @@
                   <a14:compatExt spid="_x0000_s3091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EDC6549-643B-430F-239A-CB107F1F7372}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000130C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1964,7 +2501,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>10</xdr:row>
-          <xdr:rowOff>247650</xdr:rowOff>
+          <xdr:rowOff>266700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1974,7 +2511,7 @@
                   <a14:compatExt spid="_x0000_s3095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F458C615-412D-84E9-425E-514AA13968B6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000170C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2200,7 +2737,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>247650</xdr:rowOff>
+          <xdr:rowOff>266700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2210,7 +2747,7 @@
                   <a14:compatExt spid="_x0000_s3099"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{042D0FD1-2EB2-6811-50B1-633A12558124}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2436,7 +2973,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2446,7 +2983,7 @@
                   <a14:compatExt spid="_x0000_s3103"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F19C42BC-C666-EA5D-0D4E-DF25785989EC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2672,7 +3209,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>13</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2682,7 +3219,7 @@
                   <a14:compatExt spid="_x0000_s3107"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC394520-AF7E-B2BE-BBE3-8DCB4FF0A616}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000230C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2908,7 +3445,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2918,7 +3455,7 @@
                   <a14:compatExt spid="_x0000_s3111"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00021489-1061-93A6-953A-5365AAFE248B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000270C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3144,7 +3681,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>20</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3154,7 +3691,7 @@
                   <a14:compatExt spid="_x0000_s3115"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8B7B3CA-03A3-54AB-D3F3-A1F9407A5770}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3380,7 +3917,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3390,7 +3927,7 @@
                   <a14:compatExt spid="_x0000_s3119"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DE47052-1E69-37DE-0F2A-51F65FFFB15C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3616,7 +4153,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>15</xdr:row>
-          <xdr:rowOff>247650</xdr:rowOff>
+          <xdr:rowOff>266700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3626,7 +4163,7 @@
                   <a14:compatExt spid="_x0000_s3123"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6997CAB5-9A10-0B96-1469-D7679500C23C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000330C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3852,7 +4389,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3862,7 +4399,7 @@
                   <a14:compatExt spid="_x0000_s3127"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{503D9363-7BF0-E115-1F84-EA8133E266F2}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000370C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4088,7 +4625,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>12</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4098,7 +4635,7 @@
                   <a14:compatExt spid="_x0000_s3131"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C06C0F45-638C-D1D2-093E-BB5C22C5035C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4324,7 +4861,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>15</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4334,7 +4871,7 @@
                   <a14:compatExt spid="_x0000_s3135"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ED65EAB-404E-6F43-4BF1-41D9C852074D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4559,8 +5096,8 @@
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>266700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4570,7 +5107,7 @@
                   <a14:compatExt spid="_x0000_s3139"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16A2DACF-57BB-2B56-5CC5-064F6E0A5731}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000430C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4796,7 +5333,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4806,7 +5343,7 @@
                   <a14:compatExt spid="_x0000_s3143"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED27A168-7AF6-BE63-87F1-C24295650714}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000470C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5032,7 +5569,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5042,7 +5579,7 @@
                   <a14:compatExt spid="_x0000_s3147"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08D29A51-6B0B-5E91-C6D9-76D9EA918762}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5268,7 +5805,7 @@
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>247650</xdr:rowOff>
+          <xdr:rowOff>266700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5278,7 +5815,7 @@
                   <a14:compatExt spid="_x0000_s3151"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2FF8A9C-B9A0-DC13-CFEF-260A56BAD06D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5576,7 +6113,7 @@
                   <a14:compatExt spid="_x0000_s3222"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32DC37CF-9B1B-53C0-5A01-CC3B88AEB000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000960C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5812,7 +6349,7 @@
                   <a14:compatExt spid="_x0000_s3223"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C80CC930-E1DC-36E4-5247-E352B2651754}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000970C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6048,7 +6585,7 @@
                   <a14:compatExt spid="_x0000_s3224"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BBFC4BD-BC77-1967-E49F-505394B4B2E6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000980C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6284,7 +6821,7 @@
                   <a14:compatExt spid="_x0000_s3225"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE5A49C9-487A-BA30-1EE8-1614465B786F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000990C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6520,7 +7057,7 @@
                   <a14:compatExt spid="_x0000_s3226"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1FBDE58-A0A8-384E-854E-8FBC531C3C01}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009A0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6756,7 +7293,7 @@
                   <a14:compatExt spid="_x0000_s3227"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C71A2692-F858-B2B3-2EA0-4A2BB88296D7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009B0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6992,7 +7529,7 @@
                   <a14:compatExt spid="_x0000_s3228"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DC862B3-CAD5-F6F8-88F7-251951029662}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009C0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7228,7 +7765,7 @@
                   <a14:compatExt spid="_x0000_s3229"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BD3AE2F-A303-73AC-A868-763E62779FD4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009D0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7464,7 +8001,7 @@
                   <a14:compatExt spid="_x0000_s3230"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{729EFE93-A28C-6D45-DFC1-50A577D07872}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009E0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7700,7 +8237,7 @@
                   <a14:compatExt spid="_x0000_s3231"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6C95D8A-CDE0-3CF7-30CE-CF071E8395A4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009F0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7936,7 +8473,7 @@
                   <a14:compatExt spid="_x0000_s3232"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46CCBC11-B304-0C82-F6A7-12308467D99C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A00C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8172,7 +8709,7 @@
                   <a14:compatExt spid="_x0000_s3233"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCB1A647-2B55-5D98-9685-07330F6A07CE}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A10C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8408,7 +8945,7 @@
                   <a14:compatExt spid="_x0000_s3234"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63010E85-BC82-CAA4-06B7-F02B32EE4224}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A20C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8644,7 +9181,7 @@
                   <a14:compatExt spid="_x0000_s3235"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{054649FA-28C2-9A3D-873F-A0A9A1015B1F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A30C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8880,7 +9417,7 @@
                   <a14:compatExt spid="_x0000_s3236"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D5EB227-5E1F-28CE-ABF1-6CA3FF89EB8B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A40C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -9105,8 +9642,8 @@
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>266700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9116,7 +9653,7 @@
                   <a14:compatExt spid="_x0000_s3237"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF63CC66-FCFF-7F6A-E199-F375CDB62DB4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A50C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -9352,7 +9889,7 @@
                   <a14:compatExt spid="_x0000_s3238"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEEBC261-7E61-D139-7EA8-5A7080322C43}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A60C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -9588,7 +10125,7 @@
                   <a14:compatExt spid="_x0000_s3239"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F96005DE-DCDF-9E26-9122-81CBD7050ABD}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A70C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -9824,7 +10361,7 @@
                   <a14:compatExt spid="_x0000_s3240"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F821AC40-43E7-C1B4-D56A-3B2A08BC7F92}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A80C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10060,7 +10597,7 @@
                   <a14:compatExt spid="_x0000_s3241"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42B4C3E7-4468-4465-7C72-C620644D88F4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A90C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10357,7 +10894,7 @@
                   <a14:compatExt spid="_x0000_s3242"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7880818-40FA-142E-8B9B-286E47915B5B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AA0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10949,12 +11486,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2E46626-8E39-4ABF-820B-C9A04DCE8100}">
   <sheetPr codeName="Planilha3"/>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="28.42578125" customWidth="1"/>
     <col min="5" max="5" width="31.42578125" customWidth="1"/>
-    <col min="8" max="8" width="32.140625" customWidth="1"/>
+    <col min="8" max="8" width="44.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="40.140625" customWidth="1"/>
     <col min="10" max="10" width="123.28515625" customWidth="1"/>
   </cols>
@@ -10964,13 +11501,13 @@
         <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>86</v>
@@ -10987,10 +11524,10 @@
       <c r="I1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
@@ -10999,10 +11536,10 @@
       <c r="B2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="6">
+      <c r="C2" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -11025,21 +11562,21 @@
         <v>('1','Garrafa de água mineral (500ml)','3.00','80','../img/agua.jpg','img/agua.jpg'),</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="4">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
@@ -11048,14 +11585,14 @@
         <v>30</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="J3" s="2" t="str">
-        <f t="shared" ref="J3:J21" si="0">"('"&amp;D3&amp;"',"&amp;"'"&amp;E3&amp;"',"&amp;"'"&amp;F3&amp;"',"&amp;"'"&amp;G3&amp;"',"&amp;"'"&amp;H3&amp;"',"&amp;"'"&amp;I3&amp;"'),"</f>
-        <v>('2','Garrafa de chá gelado (500ml)','5.00','30','../img/chagelado.jpg','img/chagelado.jpg'),</v>
+        <f t="shared" ref="J3:J65" si="0">"('"&amp;D3&amp;"',"&amp;"'"&amp;E3&amp;"',"&amp;"'"&amp;F3&amp;"',"&amp;"'"&amp;G3&amp;"',"&amp;"'"&amp;H3&amp;"',"&amp;"'"&amp;I3&amp;"'),"</f>
+        <v>('2','Garrafa de chá gelado  Pessego (1,5l)','5.00','30','../img/chagelado.jpg','img/chagelado.jpg'),</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -11066,13 +11603,13 @@
         <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D4" s="2">
         <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>36</v>
@@ -11099,7 +11636,7 @@
         <v>39</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
@@ -11132,9 +11669,9 @@
         <v>49</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="7">
+        <v>99</v>
+      </c>
+      <c r="D6" s="5">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -11165,7 +11702,7 @@
         <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
@@ -11198,7 +11735,7 @@
         <v>58</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2">
         <v>6</v>
@@ -11231,7 +11768,7 @@
         <v>66</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D9" s="2">
         <v>7</v>
@@ -11264,7 +11801,7 @@
         <v>82</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -11297,7 +11834,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D11" s="2">
         <v>9</v>
@@ -11330,7 +11867,7 @@
         <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" s="2">
         <v>10</v>
@@ -11362,10 +11899,10 @@
       <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="4">
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -11396,7 +11933,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14" s="2">
         <v>13</v>
@@ -11429,7 +11966,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15" s="2">
         <v>14</v>
@@ -11462,7 +11999,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D16" s="2">
         <v>14</v>
@@ -11495,7 +12032,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" s="2">
         <v>13</v>
@@ -11528,7 +12065,7 @@
         <v>62</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D18" s="2">
         <v>14</v>
@@ -11561,7 +12098,7 @@
         <v>70</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" s="2">
         <v>13</v>
@@ -11594,7 +12131,7 @@
         <v>74</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D20" s="2">
         <v>13</v>
@@ -11627,7 +12164,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" s="2">
         <v>15</v>
@@ -11650,6 +12187,1671 @@
       <c r="J21" s="2" t="str">
         <f t="shared" si="0"/>
         <v>('15','Suco natural de laranja','6.00','20','../img/suco.jpg','img/suco.jpg'),</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22" t="str">
+        <f>E22</f>
+        <v>Kitcat</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="3">
+        <v>30</v>
+      </c>
+      <c r="H22" t="str">
+        <f>_xlfn.XLOOKUP(E22,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/kitcat.jpg </v>
+      </c>
+      <c r="I22" t="str">
+        <f>_xlfn.XLOOKUP(E22,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/kitcat.jpg </v>
+      </c>
+      <c r="J22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Kitcat','5.00','30','../img/kitcat.jpg ','img/kitcat.jpg '),</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="3">
+        <v>50</v>
+      </c>
+      <c r="H23" t="str">
+        <f>_xlfn.XLOOKUP(E23,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento avelas.jpg </v>
+      </c>
+      <c r="I23" t="str">
+        <f>_xlfn.XLOOKUP(E23,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento avelas.jpg </v>
+      </c>
+      <c r="J23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Avelã','8.50','50','../img/trento avelas.jpg ','img/trento avelas.jpg '),</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="3">
+        <v>50</v>
+      </c>
+      <c r="H24" t="str">
+        <f>_xlfn.XLOOKUP(E24,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento dark.jpg </v>
+      </c>
+      <c r="I24" t="str">
+        <f>_xlfn.XLOOKUP(E24,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento dark.jpg </v>
+      </c>
+      <c r="J24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Drak','8.50','50','../img/trento dark.jpg ','img/trento dark.jpg '),</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G25" s="3">
+        <v>50</v>
+      </c>
+      <c r="H25" t="str">
+        <f>_xlfn.XLOOKUP(E25,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento Caramelo.jpg </v>
+      </c>
+      <c r="I25" t="str">
+        <f>_xlfn.XLOOKUP(E25,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento Caramelo.jpg </v>
+      </c>
+      <c r="J25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Camarelo','8.50','50','../img/trento Caramelo.jpg ','img/trento Caramelo.jpg '),</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G26" s="3">
+        <v>50</v>
+      </c>
+      <c r="H26" t="str">
+        <f>_xlfn.XLOOKUP(E26,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento morango.jpg </v>
+      </c>
+      <c r="I26" t="str">
+        <f>_xlfn.XLOOKUP(E26,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento morango.jpg </v>
+      </c>
+      <c r="J26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Morango','8.50','50','../img/trento morango.jpg ','img/trento morango.jpg '),</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G27" s="3">
+        <v>50</v>
+      </c>
+      <c r="H27" t="str">
+        <f>_xlfn.XLOOKUP(E27,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento cheese morango.jpg </v>
+      </c>
+      <c r="I27" t="str">
+        <f>_xlfn.XLOOKUP(E27,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento cheese morango.jpg </v>
+      </c>
+      <c r="J27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Cheesse Morango','8.50','50','../img/trento cheese morango.jpg ','img/trento cheese morango.jpg '),</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G28" s="3">
+        <v>50</v>
+      </c>
+      <c r="H28" t="str">
+        <f>_xlfn.XLOOKUP(E28,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento chocolate 38.jpg </v>
+      </c>
+      <c r="I28" t="str">
+        <f>_xlfn.XLOOKUP(E28,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento chocolate 38.jpg </v>
+      </c>
+      <c r="J28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Chocolate','8.50','50','../img/trento chocolate 38.jpg ','img/trento chocolate 38.jpg '),</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="3">
+        <v>50</v>
+      </c>
+      <c r="H29" t="str">
+        <f>_xlfn.XLOOKUP(E29,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento branco-drak.jpg </v>
+      </c>
+      <c r="I29" t="str">
+        <f>_xlfn.XLOOKUP(E29,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento branco-drak.jpg </v>
+      </c>
+      <c r="J29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Branco Dark','8.50','50','../img/trento branco-drak.jpg ','img/trento branco-drak.jpg '),</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3</v>
+      </c>
+      <c r="E30" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" s="3">
+        <v>50</v>
+      </c>
+      <c r="H30" t="str">
+        <f>_xlfn.XLOOKUP(E30,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento duo.jpg </v>
+      </c>
+      <c r="I30" t="str">
+        <f>_xlfn.XLOOKUP(E30,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento duo.jpg </v>
+      </c>
+      <c r="J30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Duo','8.50','50','../img/trento duo.jpg ','img/trento duo.jpg '),</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" s="3">
+        <v>50</v>
+      </c>
+      <c r="H31" t="str">
+        <f>_xlfn.XLOOKUP(E31,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento limao.jpg </v>
+      </c>
+      <c r="I31" t="str">
+        <f>_xlfn.XLOOKUP(E31,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento limao.jpg </v>
+      </c>
+      <c r="J31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Limão','8.50','50','../img/trento limao.jpg ','img/trento limao.jpg '),</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2">
+        <v>3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" s="3">
+        <v>50</v>
+      </c>
+      <c r="H32" t="str">
+        <f>_xlfn.XLOOKUP(E32,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento maracuja.jpg </v>
+      </c>
+      <c r="I32" t="str">
+        <f>_xlfn.XLOOKUP(E32,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento maracuja.jpg </v>
+      </c>
+      <c r="J32" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Maracujá','8.50','50','../img/trento maracuja.jpg ','img/trento maracuja.jpg '),</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3</v>
+      </c>
+      <c r="E33" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G33" s="3">
+        <v>50</v>
+      </c>
+      <c r="H33" t="str">
+        <f>_xlfn.XLOOKUP(E33,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento milk.jpg </v>
+      </c>
+      <c r="I33" t="str">
+        <f>_xlfn.XLOOKUP(E33,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento milk.jpg </v>
+      </c>
+      <c r="J33" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Milk','8.50','50','../img/trento milk.jpg ','img/trento milk.jpg '),</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" s="2">
+        <v>3</v>
+      </c>
+      <c r="E34" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G34" s="3">
+        <v>50</v>
+      </c>
+      <c r="H34" t="str">
+        <f>_xlfn.XLOOKUP(E34,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento trufa Maçã .jpg </v>
+      </c>
+      <c r="I34" t="str">
+        <f>_xlfn.XLOOKUP(E34,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento trufa Maçã.jpg </v>
+      </c>
+      <c r="J34" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Trufa de Maçã','8.50','50','../img/trento trufa Maçã .jpg ','img/trento trufa Maçã.jpg '),</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" t="s">
+        <v>120</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G35" s="3">
+        <v>50</v>
+      </c>
+      <c r="H35" t="str">
+        <f>_xlfn.XLOOKUP(E35,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/trento turfa de chocolate.jpg </v>
+      </c>
+      <c r="I35" t="str">
+        <f>_xlfn.XLOOKUP(E35,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/trento turfa de chocolate.jpg </v>
+      </c>
+      <c r="J35" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Trento Trufa de Chocolate','8.50','50','../img/trento turfa de chocolate.jpg ','img/trento turfa de chocolate.jpg '),</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C36">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="3">
+        <v>100</v>
+      </c>
+      <c r="H36" t="str">
+        <f>_xlfn.XLOOKUP(E36,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/barra nutry avela.jpg </v>
+      </c>
+      <c r="I36" t="str">
+        <f>_xlfn.XLOOKUP(E36,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/barra nutry avela.jpg </v>
+      </c>
+      <c r="J36" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('16','Barra Nutry Avelãs','6.00','100','../img/barra nutry avela.jpg ','img/barra nutry avela.jpg '),</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C37">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="3">
+        <v>100</v>
+      </c>
+      <c r="H37" t="str">
+        <f>_xlfn.XLOOKUP(E37,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/barra nutry banana.jpg </v>
+      </c>
+      <c r="I37" t="str">
+        <f>_xlfn.XLOOKUP(E37,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/barra nutry banana.jpg </v>
+      </c>
+      <c r="J37" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('16','Barra Nutry Banana','6.00','100','../img/barra nutry banana.jpg ','img/barra nutry banana.jpg '),</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C38">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2">
+        <v>16</v>
+      </c>
+      <c r="E38" t="s">
+        <v>124</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="3">
+        <v>100</v>
+      </c>
+      <c r="H38" t="str">
+        <f>_xlfn.XLOOKUP(E38,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/barra nutry caju.jpg </v>
+      </c>
+      <c r="I38" t="str">
+        <f>_xlfn.XLOOKUP(E38,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/barra nutry caju.jpg </v>
+      </c>
+      <c r="J38" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('16','Barra Nutry Cajú','6.00','100','../img/barra nutry caju.jpg ','img/barra nutry caju.jpg '),</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2">
+        <v>16</v>
+      </c>
+      <c r="E39" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="3">
+        <v>100</v>
+      </c>
+      <c r="H39" t="str">
+        <f>_xlfn.XLOOKUP(E39,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/barra nutry cappuccino.jpg </v>
+      </c>
+      <c r="I39" t="str">
+        <f>_xlfn.XLOOKUP(E39,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/barra nutry cappuccino.jpg </v>
+      </c>
+      <c r="J39" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('16','Barra Nutry Cappucino','6.00','100','../img/barra nutry cappuccino.jpg ','img/barra nutry cappuccino.jpg '),</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C40">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2">
+        <v>16</v>
+      </c>
+      <c r="E40" t="s">
+        <v>126</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="3">
+        <v>100</v>
+      </c>
+      <c r="H40" t="str">
+        <f>_xlfn.XLOOKUP(E40,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/barra nutry coco.jpg </v>
+      </c>
+      <c r="I40" t="str">
+        <f>_xlfn.XLOOKUP(E40,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/barra nutry coco.jpg </v>
+      </c>
+      <c r="J40" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('16','Barra Nutry Coco','6.00','100','../img/barra nutry coco.jpg ','img/barra nutry coco.jpg '),</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C41">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2">
+        <v>16</v>
+      </c>
+      <c r="E41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="3">
+        <v>100</v>
+      </c>
+      <c r="H41" t="str">
+        <f>_xlfn.XLOOKUP(E41,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/barra nutry cookies.jpg </v>
+      </c>
+      <c r="I41" t="str">
+        <f>_xlfn.XLOOKUP(E41,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/barra nutry cookies.jpg </v>
+      </c>
+      <c r="J41" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('16','Barra Nutry Cookies','6.00','100','../img/barra nutry cookies.jpg ','img/barra nutry cookies.jpg '),</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C42">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2">
+        <v>16</v>
+      </c>
+      <c r="E42" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="3">
+        <v>100</v>
+      </c>
+      <c r="H42" t="str">
+        <f>_xlfn.XLOOKUP(E42,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/barra nutry frutas-vermelhas.jpg </v>
+      </c>
+      <c r="I42" t="str">
+        <f>_xlfn.XLOOKUP(E42,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/barra nutry frutas-vermelhas.jpg </v>
+      </c>
+      <c r="J42" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('16','Barra Nutry Frutas- Vermelhas','6.00','100','../img/barra nutry frutas-vermelhas.jpg ','img/barra nutry frutas-vermelhas.jpg '),</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C43">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2">
+        <v>16</v>
+      </c>
+      <c r="E43" t="s">
+        <v>122</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" t="str">
+        <f>_xlfn.XLOOKUP(E43,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/barra nutry morango.jpg </v>
+      </c>
+      <c r="I43" t="str">
+        <f>_xlfn.XLOOKUP(E43,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/barra nutry morango.jpg </v>
+      </c>
+      <c r="J43" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('16','Barra Nutry Morango','6.00','100','../img/barra nutry morango.jpg ','img/barra nutry morango.jpg '),</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>6</v>
+      </c>
+      <c r="E44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G44" s="3">
+        <v>30</v>
+      </c>
+      <c r="H44" t="str">
+        <f>_xlfn.XLOOKUP(E44,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/nikito chocolate.jpeg </v>
+      </c>
+      <c r="I44" t="str">
+        <f>_xlfn.XLOOKUP(E44,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/nikito chocolate.jpeg </v>
+      </c>
+      <c r="J44" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('6','Biscoito  Nikito Chocolate ','18.00','30','../img/nikito chocolate.jpeg ','img/nikito chocolate.jpeg '),</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2">
+        <v>6</v>
+      </c>
+      <c r="E45" t="s">
+        <v>130</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G45" s="3">
+        <v>30</v>
+      </c>
+      <c r="H45" t="str">
+        <f>_xlfn.XLOOKUP(E45,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/nikito doce leite.jpeg </v>
+      </c>
+      <c r="I45" t="str">
+        <f>_xlfn.XLOOKUP(E45,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/nikito doce leite.jpeg </v>
+      </c>
+      <c r="J45" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('6','Biscoito  Nikito Doce de Leite','18.00','30','../img/nikito doce leite.jpeg ','img/nikito doce leite.jpeg '),</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>6</v>
+      </c>
+      <c r="E46" t="s">
+        <v>131</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G46" s="3">
+        <v>30</v>
+      </c>
+      <c r="H46" t="str">
+        <f>_xlfn.XLOOKUP(E46,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/nikito morango.jpeg </v>
+      </c>
+      <c r="I46" t="str">
+        <f>_xlfn.XLOOKUP(E46,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/nikito morango.jpeg </v>
+      </c>
+      <c r="J46" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('6','Biscoito  Nikito Morango','18.00','30','../img/nikito morango.jpeg ','img/nikito morango.jpeg '),</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2">
+        <v>4</v>
+      </c>
+      <c r="E47" t="s">
+        <v>134</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="3">
+        <v>50</v>
+      </c>
+      <c r="H47" t="str">
+        <f>_xlfn.XLOOKUP(E47,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/tubes fini azedinhos fru_silveste.jpg </v>
+      </c>
+      <c r="I47" t="str">
+        <f>_xlfn.XLOOKUP(E47,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/tubes fini azedinhos fru_silveste.jpg </v>
+      </c>
+      <c r="J47" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('4','Tubes Fini Azedinhos Furtas Silveste','7.50','50','../img/tubes fini azedinhos fru_silveste.jpg ','img/tubes fini azedinhos fru_silveste.jpg '),</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2">
+        <v>4</v>
+      </c>
+      <c r="E48" t="s">
+        <v>135</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="3">
+        <v>50</v>
+      </c>
+      <c r="H48" t="str">
+        <f>_xlfn.XLOOKUP(E48,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/tubes fini azedinhos tuttifrutti.jpg </v>
+      </c>
+      <c r="I48" t="str">
+        <f>_xlfn.XLOOKUP(E48,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/tubes fini azedinhos tuttifrutti.jpg </v>
+      </c>
+      <c r="J48" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('4','Tubes Fini Azedinhos Tutti-Frutti','7.50','50','../img/tubes fini azedinhos tuttifrutti.jpg ','img/tubes fini azedinhos tuttifrutti.jpg '),</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2">
+        <v>4</v>
+      </c>
+      <c r="E49" t="s">
+        <v>136</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="3">
+        <v>50</v>
+      </c>
+      <c r="H49" t="str">
+        <f>_xlfn.XLOOKUP(E49,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/tubes fini azedinhos uva.jpg </v>
+      </c>
+      <c r="I49" t="str">
+        <f>_xlfn.XLOOKUP(E49,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/tubes fini azedinhos uva.jpg </v>
+      </c>
+      <c r="J49" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('4','Tubes Fini Azedinhos Uva','7.50','50','../img/tubes fini azedinhos uva.jpg ','img/tubes fini azedinhos uva.jpg '),</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>137</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="3">
+        <v>50</v>
+      </c>
+      <c r="H50" t="str">
+        <f>_xlfn.XLOOKUP(E50,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/Melancia Azedinha fini.jpg </v>
+      </c>
+      <c r="I50" t="str">
+        <f>_xlfn.XLOOKUP(E50,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/Melancia Azedinha fini.jpg </v>
+      </c>
+      <c r="J50" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('4','Melancia Azedinha Fini','7.50','50','../img/Melancia Azedinha fini.jpg ','img/Melancia Azedinha fini.jpg '),</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
+        <v>138</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="3">
+        <v>50</v>
+      </c>
+      <c r="H51" t="str">
+        <f>_xlfn.XLOOKUP(E51,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/fini Dentaduras.jpg </v>
+      </c>
+      <c r="I51" t="str">
+        <f>_xlfn.XLOOKUP(E51,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/fini Dentaduras.jpg </v>
+      </c>
+      <c r="J51" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('4','Dentaduras Fini','7.50','50','../img/fini Dentaduras.jpg ','img/fini Dentaduras.jpg '),</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
+        <v>139</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="3">
+        <v>50</v>
+      </c>
+      <c r="H52" t="str">
+        <f>_xlfn.XLOOKUP(E52,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/finiMinhocas.jpg </v>
+      </c>
+      <c r="I52" t="str">
+        <f>_xlfn.XLOOKUP(E52,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/finiMinhocas.jpg </v>
+      </c>
+      <c r="J52" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('4','Minhocas Fini','7.50','50','../img/finiMinhocas.jpg ','img/finiMinhocas.jpg '),</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
+        <v>140</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="3">
+        <v>50</v>
+      </c>
+      <c r="H53" t="str">
+        <f>_xlfn.XLOOKUP(E53,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/Bala Fini amora.jpg </v>
+      </c>
+      <c r="I53" t="str">
+        <f>_xlfn.XLOOKUP(E53,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/Bala Fini amora.jpg </v>
+      </c>
+      <c r="J53" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('4','Bala Gelatina Amoras Fini','7.50','50','../img/Bala Fini amora.jpg ','img/Bala Fini amora.jpg '),</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
+        <v>141</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G54" s="3">
+        <v>50</v>
+      </c>
+      <c r="H54" t="str">
+        <f>_xlfn.XLOOKUP(E54,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/bala gelatina fini.jpg </v>
+      </c>
+      <c r="I54" t="str">
+        <f>_xlfn.XLOOKUP(E54,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/bala gelatina fini.jpg </v>
+      </c>
+      <c r="J54" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('4','Bala Gelatina Beijos Fini','7.50','50','../img/bala gelatina fini.jpg ','img/bala gelatina fini.jpg '),</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>142</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G55" s="3">
+        <v>50</v>
+      </c>
+      <c r="H55" t="str">
+        <f>_xlfn.XLOOKUP(E55,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/Bala Gelatina Finiburguers Fini.jpg </v>
+      </c>
+      <c r="I55" t="str">
+        <f>_xlfn.XLOOKUP(E55,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/Bala Gelatina Finiburguers Fini.jpg </v>
+      </c>
+      <c r="J55" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('4','Bala Gelatina Finiburguers Fini','7.50','50','../img/Bala Gelatina Finiburguers Fini.jpg ','img/Bala Gelatina Finiburguers Fini.jpg '),</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>143</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G56" s="3">
+        <v>50</v>
+      </c>
+      <c r="H56" t="str">
+        <f>_xlfn.XLOOKUP(E56,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/Bala Gelatinas Polvo 80g FINI.jpg </v>
+      </c>
+      <c r="I56" t="str">
+        <f>_xlfn.XLOOKUP(E56,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/Bala Gelatinas Polvo 80g FINI.jpg </v>
+      </c>
+      <c r="J56" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('4','Bala Gelatinas Polvo Fini','7.50','50','../img/Bala Gelatinas Polvo 80g FINI.jpg ','img/Bala Gelatinas Polvo 80g FINI.jpg '),</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57" s="2">
+        <v>3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>144</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G57" s="3">
+        <v>100</v>
+      </c>
+      <c r="H57" t="str">
+        <f>_xlfn.XLOOKUP(E57,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/sonhodevalsa.jpeg </v>
+      </c>
+      <c r="I57" t="str">
+        <f>_xlfn.XLOOKUP(E57,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/sonhodevalsa.jpeg </v>
+      </c>
+      <c r="J57" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Sonho de Valsa','2.50','100','../img/sonhodevalsa.jpeg ','img/sonhodevalsa.jpeg '),</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58" s="2">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>145</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="3">
+        <v>100</v>
+      </c>
+      <c r="H58" t="str">
+        <f>_xlfn.XLOOKUP(E58,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/ouro branco.jpeg </v>
+      </c>
+      <c r="I58" t="str">
+        <f>_xlfn.XLOOKUP(E58,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/ouro branco.jpeg </v>
+      </c>
+      <c r="J58" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Ouro Branco','2.50','100','../img/ouro branco.jpeg ','img/ouro branco.jpeg '),</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59" s="2">
+        <v>3</v>
+      </c>
+      <c r="E59" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G59" s="3">
+        <v>50</v>
+      </c>
+      <c r="H59" t="str">
+        <f>_xlfn.XLOOKUP(E59,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/Bis.jpeg </v>
+      </c>
+      <c r="I59" t="str">
+        <f>_xlfn.XLOOKUP(E59,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/Bis.jpeg </v>
+      </c>
+      <c r="J59" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('3','Bis Xtra','18.00','50','../img/Bis.jpeg ','img/Bis.jpeg '),</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C60">
+        <v>7</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2</v>
+      </c>
+      <c r="E60" t="s">
+        <v>147</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G60" s="3">
+        <v>30</v>
+      </c>
+      <c r="H60" t="str">
+        <f>_xlfn.XLOOKUP(E60,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/cha mate limão.jpeg </v>
+      </c>
+      <c r="I60" t="str">
+        <f>_xlfn.XLOOKUP(E60,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/cha mate limão.jpeg </v>
+      </c>
+      <c r="J60" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('2','Chá Mate Leão Limão','3.19','30','../img/cha mate limão.jpeg ','img/cha mate limão.jpeg '),</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
+      </c>
+      <c r="D61" s="2">
+        <v>2</v>
+      </c>
+      <c r="E61" t="s">
+        <v>148</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G61" s="3">
+        <v>30</v>
+      </c>
+      <c r="H61" t="str">
+        <f>_xlfn.XLOOKUP(E61,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/cha mate pessego.jpeg </v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.XLOOKUP(E61,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/cha mate pessego.jpeg </v>
+      </c>
+      <c r="J61" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('2','Chá Mate Leão Pessego','3.19','30','../img/cha mate pessego.jpeg ','img/cha mate pessego.jpeg '),</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>205</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G62" s="3">
+        <v>20</v>
+      </c>
+      <c r="H62" t="str">
+        <f>_xlfn.XLOOKUP(E62,Planilha1!A:A,Planilha1!B:B)</f>
+        <v>../img/coca-cola.jpeg</v>
+      </c>
+      <c r="I62" t="str">
+        <f>_xlfn.XLOOKUP(E62,Planilha1!A:A,Planilha1!C:C)</f>
+        <v>img/coca-cola.jpeg</v>
+      </c>
+      <c r="J62" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('11','Coca-Cola','4.20','20','../img/coca-cola.jpeg','img/coca-cola.jpeg'),</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>206</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G63" s="3">
+        <v>20</v>
+      </c>
+      <c r="H63" t="str">
+        <f>_xlfn.XLOOKUP(E63,Planilha1!A:A,Planilha1!B:B)</f>
+        <v>../img/coca-cola zero.jpeg</v>
+      </c>
+      <c r="I63" t="str">
+        <f>_xlfn.XLOOKUP(E63,Planilha1!A:A,Planilha1!C:C)</f>
+        <v>img/coca-cola zero.jpeg</v>
+      </c>
+      <c r="J63" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('11','Coca-Cola Zero','4.20','20','../img/coca-cola zero.jpeg','img/coca-cola zero.jpeg'),</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>207</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G64" s="3">
+        <v>15</v>
+      </c>
+      <c r="H64" t="str">
+        <f>_xlfn.XLOOKUP(E64,Planilha1!A:A,Planilha1!B:B)</f>
+        <v>../img/sprite.jpeg</v>
+      </c>
+      <c r="I64" t="str">
+        <f>_xlfn.XLOOKUP(E64,Planilha1!A:A,Planilha1!C:C)</f>
+        <v>img/sprite.jpeg</v>
+      </c>
+      <c r="J64" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('11','Sprite','3.69','15','../img/sprite.jpeg','img/sprite.jpeg'),</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>209</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G65" s="3">
+        <v>20</v>
+      </c>
+      <c r="H65" t="str">
+        <f>_xlfn.XLOOKUP(E65,Planilha1!A:A,Planilha1!B:B)</f>
+        <v>../img/fanta.jpeg</v>
+      </c>
+      <c r="I65" t="str">
+        <f>_xlfn.XLOOKUP(E65,Planilha1!A:A,Planilha1!C:C)</f>
+        <v>img/fanta.jpeg</v>
+      </c>
+      <c r="J65" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>('11','Fanta Laranja','4.70','20','../img/fanta.jpeg','img/fanta.jpeg'),</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>208</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G66" s="3">
+        <v>20</v>
+      </c>
+      <c r="H66" t="str">
+        <f>_xlfn.XLOOKUP(E66,Planilha1!A:A,Planilha1!B:B)</f>
+        <v>../img/fanta uva.jpeg</v>
+      </c>
+      <c r="I66" t="str">
+        <f>_xlfn.XLOOKUP(E66,Planilha1!A:A,Planilha1!C:C)</f>
+        <v>img/fanta uva.jpeg</v>
+      </c>
+      <c r="J66" s="2" t="str">
+        <f t="shared" ref="J66:J72" si="1">"('"&amp;D66&amp;"',"&amp;"'"&amp;E66&amp;"',"&amp;"'"&amp;F66&amp;"',"&amp;"'"&amp;G66&amp;"',"&amp;"'"&amp;H66&amp;"',"&amp;"'"&amp;I66&amp;"'),"</f>
+        <v>('11','Fanta Uva','3.99','20','../img/fanta uva.jpeg','img/fanta uva.jpeg'),</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2">
+        <v>12</v>
+      </c>
+      <c r="E67" t="s">
+        <v>218</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G67">
+        <v>30</v>
+      </c>
+      <c r="H67" t="str">
+        <f>_xlfn.XLOOKUP(E67,Planilha1!A:A,Planilha1!B:B)</f>
+        <v>../img/coca-cola zero 500ml.jpeg</v>
+      </c>
+      <c r="I67" t="str">
+        <f>_xlfn.XLOOKUP(E67,Planilha1!A:A,Planilha1!C:C)</f>
+        <v>img/coca-cola zero 500ml.jpeg</v>
+      </c>
+      <c r="J67" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>('12','Coca-Cola Zero 500ml','6.99','30','../img/coca-cola zero 500ml.jpeg','img/coca-cola zero 500ml.jpeg'),</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2">
+        <v>12</v>
+      </c>
+      <c r="E68" t="s">
+        <v>217</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G68">
+        <v>30</v>
+      </c>
+      <c r="H68" t="str">
+        <f>_xlfn.XLOOKUP(E68,Planilha1!A:A,Planilha1!B:B)</f>
+        <v>../img/coca-cola 500ml.jpeg</v>
+      </c>
+      <c r="I68" t="str">
+        <f>_xlfn.XLOOKUP(E68,Planilha1!A:A,Planilha1!C:C)</f>
+        <v>img/coca-cola 500ml.jpeg</v>
+      </c>
+      <c r="J68" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>('12','Coca-Cola 500ml','6.99','30','../img/coca-cola 500ml.jpeg','img/coca-cola 500ml.jpeg'),</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B69" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C69">
+        <v>9</v>
+      </c>
+      <c r="D69" s="2">
+        <v>16</v>
+      </c>
+      <c r="E69" t="s">
+        <v>215</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" s="3">
+        <v>100</v>
+      </c>
+      <c r="H69" t="str">
+        <f>_xlfn.XLOOKUP(E69,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/Barra Nutry bolo_chocolate.jpg </v>
+      </c>
+      <c r="I69" t="str">
+        <f>_xlfn.XLOOKUP(E69,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/Barra Nutry bolo_chocolate.jpg </v>
+      </c>
+      <c r="J69" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>('16','Barra Nutry bolo_chocolate','6.00','100','../img/Barra Nutry bolo_chocolate.jpg ','img/Barra Nutry bolo_chocolate.jpg '),</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2">
+        <v>4</v>
+      </c>
+      <c r="E70" t="s">
+        <v>219</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G70" s="3">
+        <v>50</v>
+      </c>
+      <c r="H70" t="str">
+        <f>_xlfn.XLOOKUP(E70,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/Bala fini tubes.jpg </v>
+      </c>
+      <c r="I70" t="str">
+        <f>_xlfn.XLOOKUP(E70,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/Bala fini tubes.jpg </v>
+      </c>
+      <c r="J70" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>('4','Bala fini tubes','7.50','50','../img/Bala fini tubes.jpg ','img/Bala fini tubes.jpg '),</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B71" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2">
+        <v>4</v>
+      </c>
+      <c r="E71" t="s">
+        <v>220</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G71" s="3">
+        <v>50</v>
+      </c>
+      <c r="H71" t="str">
+        <f>_xlfn.XLOOKUP(E71,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/Bala  Bananas fini.jpg </v>
+      </c>
+      <c r="I71" t="str">
+        <f>_xlfn.XLOOKUP(E71,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/Bala  Bananas fini.jpg </v>
+      </c>
+      <c r="J71" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>('4','Bala Fini banana','7.50','50','../img/Bala  Bananas fini.jpg ','img/Bala  Bananas fini.jpg '),</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B72" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2">
+        <v>4</v>
+      </c>
+      <c r="E72" t="s">
+        <v>221</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G72" s="3">
+        <v>50</v>
+      </c>
+      <c r="H72" t="str">
+        <f>_xlfn.XLOOKUP(E72,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/Aros de Morango Azedinhos 80g - Fini.jpg </v>
+      </c>
+      <c r="I72" t="str">
+        <f>_xlfn.XLOOKUP(E72,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/Aros de Morango Azedinhos 80g - Fini.jpg </v>
+      </c>
+      <c r="J72" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>('4','Aros de Morango Azedinhos 80g','7.50','50','../img/Aros de Morango Azedinhos 80g - Fini.jpg ','img/Aros de Morango Azedinhos 80g - Fini.jpg '),</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B73" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2">
+        <v>4</v>
+      </c>
+      <c r="E73" t="s">
+        <v>222</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G73" s="3">
+        <v>50</v>
+      </c>
+      <c r="H73" t="str">
+        <f>_xlfn.XLOOKUP(E73,Planilha1!A:A,Planilha1!B:B)</f>
+        <v xml:space="preserve">../img/Bala  Escovinhas Fini.jpg </v>
+      </c>
+      <c r="I73" t="str">
+        <f>_xlfn.XLOOKUP(E73,Planilha1!A:A,Planilha1!C:C)</f>
+        <v xml:space="preserve">img/Bala  Escovinhas Fini.jpg </v>
+      </c>
+      <c r="J73" s="2" t="str">
+        <f>"('"&amp;D73&amp;"',"&amp;"'"&amp;E73&amp;"',"&amp;"'"&amp;F73&amp;"',"&amp;"'"&amp;G73&amp;"',"&amp;"'"&amp;H73&amp;"',"&amp;"'"&amp;I73&amp;"'),"</f>
+        <v>('4','Bala  Escovinhas Fini','7.50','50','../img/Bala  Escovinhas Fini.jpg ','img/Bala  Escovinhas Fini.jpg '),</v>
       </c>
     </row>
   </sheetData>
@@ -11820,8 +14022,8 @@
               <to>
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>266700</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -12209,7 +14411,7 @@
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
         <control shapeId="3151" r:id="rId32" name="Control 79">
-          <controlPr defaultSize="0" r:id="rId33">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12221,7 +14423,7 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>7</xdr:row>
-                <xdr:rowOff>247650</xdr:rowOff>
+                <xdr:rowOff>266700</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -12233,8 +14435,8 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3147" r:id="rId34" name="Control 75">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3147" r:id="rId33" name="Control 75">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12246,20 +14448,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3147" r:id="rId34" name="Control 75"/>
+        <control shapeId="3147" r:id="rId33" name="Control 75"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3143" r:id="rId35" name="Control 71">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3143" r:id="rId34" name="Control 71">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12271,20 +14473,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>4</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3143" r:id="rId35" name="Control 71"/>
+        <control shapeId="3143" r:id="rId34" name="Control 71"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3139" r:id="rId36" name="Control 67">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3139" r:id="rId35" name="Control 67">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12295,21 +14497,21 @@
               <to>
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>266700</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3139" r:id="rId36" name="Control 67"/>
+        <control shapeId="3139" r:id="rId35" name="Control 67"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3135" r:id="rId37" name="Control 63">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3135" r:id="rId36" name="Control 63">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12321,20 +14523,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>15</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3135" r:id="rId37" name="Control 63"/>
+        <control shapeId="3135" r:id="rId36" name="Control 63"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3131" r:id="rId38" name="Control 59">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3131" r:id="rId37" name="Control 59">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12346,20 +14548,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>12</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3131" r:id="rId38" name="Control 59"/>
+        <control shapeId="3131" r:id="rId37" name="Control 59"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3127" r:id="rId39" name="Control 55">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3127" r:id="rId38" name="Control 55">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12371,20 +14573,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>7</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3127" r:id="rId39" name="Control 55"/>
+        <control shapeId="3127" r:id="rId38" name="Control 55"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3123" r:id="rId40" name="Control 51">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3123" r:id="rId39" name="Control 51">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12396,20 +14598,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>15</xdr:row>
-                <xdr:rowOff>247650</xdr:rowOff>
+                <xdr:rowOff>266700</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3123" r:id="rId40" name="Control 51"/>
+        <control shapeId="3123" r:id="rId39" name="Control 51"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3119" r:id="rId41" name="Control 47">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3119" r:id="rId40" name="Control 47">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12421,20 +14623,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>18</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3119" r:id="rId41" name="Control 47"/>
+        <control shapeId="3119" r:id="rId40" name="Control 47"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3115" r:id="rId42" name="Control 43">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3115" r:id="rId41" name="Control 43">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12446,20 +14648,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>20</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3115" r:id="rId42" name="Control 43"/>
+        <control shapeId="3115" r:id="rId41" name="Control 43"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3111" r:id="rId43" name="Control 39">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3111" r:id="rId42" name="Control 39">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12471,20 +14673,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>17</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3111" r:id="rId43" name="Control 39"/>
+        <control shapeId="3111" r:id="rId42" name="Control 39"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3107" r:id="rId44" name="Control 35">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3107" r:id="rId43" name="Control 35">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12496,20 +14698,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>13</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3107" r:id="rId44" name="Control 35"/>
+        <control shapeId="3107" r:id="rId43" name="Control 35"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3103" r:id="rId45" name="Control 31">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3103" r:id="rId44" name="Control 31">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12521,20 +14723,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>6</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3103" r:id="rId45" name="Control 31"/>
+        <control shapeId="3103" r:id="rId44" name="Control 31"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3099" r:id="rId46" name="Control 27">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3099" r:id="rId45" name="Control 27">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12546,20 +14748,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>13</xdr:row>
-                <xdr:rowOff>247650</xdr:rowOff>
+                <xdr:rowOff>266700</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3099" r:id="rId46" name="Control 27"/>
+        <control shapeId="3099" r:id="rId45" name="Control 27"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3095" r:id="rId47" name="Control 23">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3095" r:id="rId46" name="Control 23">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12571,20 +14773,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>10</xdr:row>
-                <xdr:rowOff>247650</xdr:rowOff>
+                <xdr:rowOff>266700</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3095" r:id="rId47" name="Control 23"/>
+        <control shapeId="3095" r:id="rId46" name="Control 23"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3091" r:id="rId48" name="Control 19">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3091" r:id="rId47" name="Control 19">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12596,20 +14798,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>10</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3091" r:id="rId48" name="Control 19"/>
+        <control shapeId="3091" r:id="rId47" name="Control 19"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3087" r:id="rId49" name="Control 15">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3087" r:id="rId48" name="Control 15">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12621,20 +14823,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>21</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3087" r:id="rId49" name="Control 15"/>
+        <control shapeId="3087" r:id="rId48" name="Control 15"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3083" r:id="rId50" name="Control 11">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3083" r:id="rId49" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12646,20 +14848,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>19</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3083" r:id="rId50" name="Control 11"/>
+        <control shapeId="3083" r:id="rId49" name="Control 11"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3079" r:id="rId51" name="Control 7">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3079" r:id="rId50" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12671,20 +14873,20 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3079" r:id="rId51" name="Control 7"/>
+        <control shapeId="3079" r:id="rId50" name="Control 7"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3075" r:id="rId52" name="Control 3">
-          <controlPr defaultSize="0" r:id="rId33">
+        <control shapeId="3075" r:id="rId51" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -12696,16 +14898,636 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3075" r:id="rId52" name="Control 3"/>
+        <control shapeId="3075" r:id="rId51" name="Control 3"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64B06AD-FD1E-406B-9BE2-2F7E10364243}">
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="66.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C31" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C33" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C34" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C40" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C41" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C43" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C45" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C46" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C48" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C49" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C50" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C52" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C53" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C54" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C55" t="s">
+        <v>281</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>